--- a/AutoCreateSlddGuiPrototype/AutoCreateSldd_TemplateSeed.xlsx
+++ b/AutoCreateSlddGuiPrototype/AutoCreateSldd_TemplateSeed.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bus" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BusElement" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="History" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Signal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Parameter" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Bus" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="BusElement" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <bgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,12 +87,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -567,7 +573,6 @@
           <t>蓝色表头为必填列，浅蓝色表头为选填列</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>模板已内置示例数据与 Config 下拉列表，可直接改名改值后使用</t>
@@ -1037,12 +1042,12 @@
           <t>InitialValue</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>HeaderFile</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>DefinitionFile</t>
         </is>
@@ -1304,12 +1309,12 @@
           <t>InitialValue</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>HeaderFile</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>DefinitionFile</t>
         </is>
